--- a/data/trans_orig/IP11A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP11A-Clase-trans_orig.xlsx
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>57,78%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>799</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>56,71%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>526</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>482</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>56,51%</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -3796,12 +3796,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -4965,12 +4965,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -5078,12 +5078,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>71,32%</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,15%</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,9%</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -6442,12 +6442,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>485</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>482</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>20630</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>22919</t>
+          <t>23012</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>15157</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>27049</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>19014</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>18858</t>
+          <t>18724</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>32581</t>
+          <t>32670</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>63,36%</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -8683,12 +8683,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8698,12 +8698,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -8796,12 +8796,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>747</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8831,12 +8831,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>453</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8866,12 +8866,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,61%</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8979,12 +8979,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -9591,12 +9591,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>265</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9661,12 +9661,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,68%</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -9817,12 +9817,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>49,97%</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10456,12 +10456,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -10499,12 +10499,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10514,12 +10514,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10534,12 +10534,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10569,12 +10569,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22767</t>
+          <t>22229</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -10612,12 +10612,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -10627,12 +10627,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -10682,12 +10682,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -10697,12 +10697,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10740,12 +10740,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -11294,12 +11294,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -11309,12 +11309,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11442,12 +11442,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11535,12 +11535,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11555,12 +11555,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -11633,12 +11633,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11648,12 +11648,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11668,12 +11668,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10424</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -12350,12 +12350,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12385,12 +12385,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12400,12 +12400,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,54%</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12498,12 +12498,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12513,12 +12513,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -12576,12 +12576,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>60,69%</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -13052,7 +13052,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -13110,12 +13110,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13125,12 +13125,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -13160,12 +13160,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -13180,12 +13180,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -13195,12 +13195,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -13223,12 +13223,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>25505</t>
+          <t>26268</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>24687</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38168</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13273,12 +13273,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13293,12 +13293,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>42473</t>
+          <t>42005</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>60632</t>
+          <t>60091</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13308,12 +13308,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -13336,12 +13336,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>17219</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>9891</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>21583</t>
+          <t>22080</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -13406,12 +13406,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>19700</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>34575</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -13499,12 +13499,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -13519,12 +13519,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>20939</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>37132</t>
+          <t>34984</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -13534,12 +13534,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -14257,7 +14257,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14455,7 +14455,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,05%</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -14596,7 +14596,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14661,12 +14661,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14676,12 +14676,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -15235,7 +15235,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>52,09%</t>
         </is>
       </c>
     </row>
@@ -15308,12 +15308,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15323,12 +15323,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15343,12 +15343,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15358,12 +15358,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15476,7 +15476,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>50,77%</t>
         </is>
       </c>
     </row>
@@ -15539,7 +15539,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16256,7 +16256,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>56,72%</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16334,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16364,12 +16364,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16379,12 +16379,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,67%</t>
         </is>
       </c>
     </row>
@@ -16447,7 +16447,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -16642,7 +16642,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16677,7 +16677,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16933,12 +16933,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16948,12 +16948,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16996,7 +16996,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -17046,12 +17046,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -17061,12 +17061,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -17124,12 +17124,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -17139,12 +17139,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17179,7 +17179,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -17202,12 +17202,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17217,12 +17217,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17272,12 +17272,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17287,12 +17287,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -17320,7 +17320,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17350,12 +17350,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>796</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17365,12 +17365,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17385,12 +17385,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17400,12 +17400,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17846,7 +17846,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17861,7 +17861,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -17919,12 +17919,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17934,12 +17934,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -17954,12 +17954,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -17969,12 +17969,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -18037,7 +18037,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -18110,12 +18110,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -18125,12 +18125,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -18145,12 +18145,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -18160,12 +18160,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -18180,12 +18180,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -18195,12 +18195,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -18228,7 +18228,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -18298,7 +18298,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -18313,7 +18313,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18882,7 +18882,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -18940,12 +18940,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18955,12 +18955,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
@@ -18990,12 +18990,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,94%</t>
         </is>
       </c>
     </row>
@@ -19053,12 +19053,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -19068,12 +19068,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -19088,12 +19088,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -19103,12 +19103,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -19186,7 +19186,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -19366,7 +19366,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -19381,7 +19381,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -19416,7 +19416,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19431,12 +19431,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>559</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19446,12 +19446,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -19587,12 +19587,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19602,12 +19602,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19657,12 +19657,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19672,12 +19672,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -19700,12 +19700,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19715,12 +19715,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19750,12 +19750,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19770,12 +19770,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>21425</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19785,12 +19785,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -19813,12 +19813,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19828,12 +19828,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19848,12 +19848,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19863,12 +19863,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19883,12 +19883,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>20795</t>
+          <t>20827</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19898,12 +19898,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -19926,12 +19926,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -19941,12 +19941,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -19961,12 +19961,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -19976,12 +19976,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -19996,12 +19996,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>22394</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -20011,12 +20011,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -20039,12 +20039,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -20054,12 +20054,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -20074,12 +20074,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -20089,12 +20089,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -20109,12 +20109,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -20124,12 +20124,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>412</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -21040,12 +21040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -21186,7 +21186,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -21201,7 +21201,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -21221,7 +21221,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -21256,7 +21256,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -21271,7 +21271,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>63,47%</t>
         </is>
       </c>
     </row>
@@ -21677,7 +21677,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -21692,7 +21692,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -21727,7 +21727,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -21790,7 +21790,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -21820,12 +21820,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -21835,12 +21835,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>66,2%</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -21938,7 +21938,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -21953,7 +21953,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -22031,7 +22031,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -22046,12 +22046,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -22061,12 +22061,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,14%</t>
         </is>
       </c>
     </row>
@@ -22129,7 +22129,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -22144,7 +22144,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -22164,7 +22164,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -22179,7 +22179,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -22856,7 +22856,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -22959,7 +22959,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -23458,7 +23458,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -23528,7 +23528,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -23543,7 +23543,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -23571,7 +23571,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -23586,7 +23586,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -23621,7 +23621,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -23636,12 +23636,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -23651,12 +23651,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -23684,7 +23684,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -23714,12 +23714,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -23729,12 +23729,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -23764,12 +23764,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -23792,12 +23792,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -23807,12 +23807,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -23862,12 +23862,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -23877,12 +23877,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,91%</t>
         </is>
       </c>
     </row>
@@ -23945,7 +23945,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -23960,7 +23960,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -23980,7 +23980,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -24140,7 +24140,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -24155,7 +24155,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -24549,7 +24549,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -24564,7 +24564,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -24700,7 +24700,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -24715,7 +24715,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -24770,12 +24770,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -24785,12 +24785,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -24818,7 +24818,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -24833,7 +24833,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -25500,7 +25500,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -25515,7 +25515,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -25570,7 +25570,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>79,7%</t>
         </is>
       </c>
     </row>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -25956,7 +25956,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -25971,7 +25971,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -26026,7 +26026,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -26041,7 +26041,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -26182,7 +26182,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -26197,7 +26197,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -26232,7 +26232,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -26247,12 +26247,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -26262,12 +26262,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -26290,12 +26290,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -26305,12 +26305,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -26325,12 +26325,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -26340,12 +26340,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -26360,12 +26360,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -26375,12 +26375,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -26403,12 +26403,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -26418,12 +26418,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -26438,12 +26438,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -26453,12 +26453,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -26473,12 +26473,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -26488,12 +26488,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -26516,12 +26516,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -26531,12 +26531,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -26551,12 +26551,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -26566,12 +26566,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -26586,12 +26586,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -26601,12 +26601,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -26629,12 +26629,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>380</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -26644,12 +26644,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -26664,12 +26664,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -26679,12 +26679,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -26699,12 +26699,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -26714,12 +26714,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
